--- a/data/trending_integrated_20261006_11.xlsx
+++ b/data/trending_integrated_20261006_11.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52547564360</v>
+        <v>52559481520</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47450</v>
+        <v>47400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.31%</t>
+          <t>'+17.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="F3" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="G3" t="n">
-        <v>2743</v>
+        <v>2860</v>
       </c>
       <c r="H3" t="n">
         <v>14.1</v>
@@ -702,7 +702,7 @@
         <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>215453608725</v>
+        <v>216801240725</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB 간암 신약의 미국 FDA 승인 관련 AI 답변 및 공식 블로그 확인. MSCI 편입 기대감과 함께 100만원 목표가 제시.</t>
+          <t>HLB 간암 신약 美 FDA 승인 관련 AI 답변 및 블로그 공시 확인. MSCI 편입 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', 'MSCI 편입']</t>
+          <t>['FDA 승인', '간암 신약', 'MSCI']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17980</v>
+        <v>17750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.06%</t>
+          <t>'+15.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H4" t="n">
         <v>2.17</v>
@@ -794,7 +794,7 @@
         <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>65809782480</v>
+        <v>67853152505</v>
       </c>
       <c r="P4" t="n">
         <v>38400</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4980</v>
+        <v>4975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.18%</t>
+          <t>'+13.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>109814087737</v>
+        <v>111298381601</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+8.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.17</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H6" t="n">
         <v>1.09</v>
@@ -978,7 +978,7 @@
         <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>18235705941</v>
+        <v>18486940547</v>
       </c>
       <c r="P6" t="n">
         <v>2970</v>
@@ -1044,7 +1044,7 @@
         <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H7" t="n">
         <v>1.82</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>35003383160</v>
+        <v>35494518379</v>
       </c>
       <c r="P7" t="n">
         <v>4810</v>
@@ -1130,13 +1130,13 @@
         <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
@@ -1162,7 +1162,7 @@
         <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>119381513090</v>
+        <v>120141104590</v>
       </c>
       <c r="P8" t="n">
         <v>30550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18410</v>
+        <v>18390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.43%</t>
+          <t>'+3.31%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>470</v>
+        <v>523</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>177223266455</v>
+        <v>180531444630</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세와 국내 대장주로서의 기대감. 2만원 돌파를 목표로 매물 소화 과정이라는 분석.</t>
+          <t>미국 증시 광통신 섹터 강세 및 루멘텀, 어플라이드옵토 등 동반 강세. 매물대 소화 및 2만원 돌파 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '섹터', '대장주']</t>
+          <t>['광통신', '매물대', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17770</v>
+        <v>17820</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.91%</t>
+          <t>'+1.19%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="H10" t="n">
         <v>9.390000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>37204802745</v>
+        <v>38714383335</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>275500</v>
+        <v>274250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.18%</t>
+          <t>'-0.63%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F11" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G11" t="n">
-        <v>2238</v>
+        <v>2251</v>
       </c>
       <c r="H11" t="n">
         <v>46.41</v>
@@ -1432,13 +1432,13 @@
         <v>279000</v>
       </c>
       <c r="M11" t="n">
-        <v>274500</v>
+        <v>274000</v>
       </c>
       <c r="N11" t="n">
         <v>46.41</v>
       </c>
       <c r="O11" t="n">
-        <v>1399605611750</v>
+        <v>1438919410000</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 시장 랠리 및 외국인 수급 기대감 속 3분기 영업이익 전망. 일부 정치적 언급 및 타사 주가 비교 내용 포함.</t>
+          <t>미국 증시 및 엔비디아 신고가 경신에 따른 반도체 시장 훈풍 기대감. 일부 부정적 뉴스 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '영업이익', '외국인 수급']</t>
+          <t>['반도체', '엔비디아', '영업이익']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1797000</v>
+        <v>1793000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-2.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G12" t="n">
-        <v>2198</v>
+        <v>2062</v>
       </c>
       <c r="H12" t="n">
         <v>49.76</v>
@@ -1530,7 +1530,7 @@
         <v>49.77</v>
       </c>
       <c r="O12" t="n">
-        <v>1870121899500</v>
+        <v>1946047046500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 증시 AI 열풍에도 불구하고 메모리 반도체 부진 및 솔리다임 상장 이슈로 인한 주가 약세.</t>
+          <t>엔비디아 및 미국 증시 신고가 경신에도 불구하고 메모리 관련주는 하락하는 모습. 일부 투자자 부정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['메모리 반도체', 'AI', '솔리다임']</t>
+          <t>['메모리', '엔비디아', '미국 증시']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261006_11.xlsx
+++ b/data/trending_integrated_20261006_11.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52559481520</v>
+        <v>52561745260</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47400</v>
+        <v>18370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.18%</t>
+          <t>'+19.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>559</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>358</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>2860</v>
+        <v>63</v>
       </c>
       <c r="H3" t="n">
-        <v>14.1</v>
+        <v>2.17</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40450</v>
+        <v>15360</v>
       </c>
       <c r="K3" t="n">
-        <v>42700</v>
+        <v>18000</v>
       </c>
       <c r="L3" t="n">
-        <v>50700</v>
+        <v>18540</v>
       </c>
       <c r="M3" t="n">
-        <v>42150</v>
+        <v>16800</v>
       </c>
       <c r="N3" t="n">
-        <v>14.11</v>
+        <v>1.37</v>
       </c>
       <c r="O3" t="n">
-        <v>216801240725</v>
+        <v>74503123255</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>38400</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>8010</v>
       </c>
       <c r="R3" t="n">
-        <v>477000</v>
+        <v>41000</v>
       </c>
       <c r="S3" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 美 FDA 승인 관련 AI 답변 및 블로그 공시 확인. MSCI 편입 기대감.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', 'MSCI']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17750</v>
+        <v>47800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.56%</t>
+          <t>'+18.17%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>576</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>366</v>
       </c>
       <c r="G4" t="n">
-        <v>62</v>
+        <v>2980</v>
       </c>
       <c r="H4" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K4" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L4" t="n">
-        <v>18500</v>
+        <v>50700</v>
       </c>
       <c r="M4" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N4" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>67853152505</v>
+        <v>218854439775</v>
       </c>
       <c r="P4" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>41000</v>
+        <v>477000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>HLB 간암 신약 FDA 승인 관련 긍정적 소식과 MSCI 편입 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['FDA 승인', '간암 신약', 'MSCI 편입']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4975</v>
+        <v>4915</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.07%</t>
+          <t>'+11.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>111298381601</v>
+        <v>114954957711</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -931,162 +931,162 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1455</v>
+        <v>20550</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.58%</t>
+          <t>'+9.37%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1340</v>
+        <v>18790</v>
       </c>
       <c r="K6" t="n">
-        <v>1370</v>
+        <v>21400</v>
       </c>
       <c r="L6" t="n">
-        <v>1555</v>
+        <v>22300</v>
       </c>
       <c r="M6" t="n">
-        <v>1360</v>
+        <v>20050</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>0.83</v>
       </c>
       <c r="O6" t="n">
-        <v>18486940547</v>
+        <v>122053396740</v>
       </c>
       <c r="P6" t="n">
-        <v>2970</v>
+        <v>30550</v>
       </c>
       <c r="Q6" t="n">
-        <v>890</v>
+        <v>6100</v>
       </c>
       <c r="R6" t="n">
-        <v>-15000</v>
+        <v>-64000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
+          <t>대통령 지시로 주목받는 보안주 섹터의 수혜 기대. 금융 고객사 확보 및 샌즈랩, 안랩 등 타 종목 동반 상승 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['LNG', '송유관', '테마']</t>
+          <t>['보안주', '금융고객사', '샌즈랩']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3055</v>
+        <v>1454</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.38%</t>
+          <t>'+8.51%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.57</v>
+        <v>-0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2845</v>
+        <v>1340</v>
       </c>
       <c r="K7" t="n">
-        <v>3200</v>
+        <v>1370</v>
       </c>
       <c r="L7" t="n">
-        <v>3360</v>
+        <v>1555</v>
       </c>
       <c r="M7" t="n">
-        <v>2995</v>
+        <v>1360</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>35494518379</v>
+        <v>18560687332</v>
       </c>
       <c r="P7" t="n">
-        <v>4810</v>
+        <v>2970</v>
       </c>
       <c r="Q7" t="n">
-        <v>1400</v>
+        <v>890</v>
       </c>
       <c r="R7" t="n">
-        <v>-8000</v>
+        <v>-15000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
+          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CB', '차익실현', '공매도']</t>
+          <t>['LNG', '송유관', '테마']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20150</v>
+        <v>3085</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.24%</t>
+          <t>'+8.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18790</v>
+        <v>2845</v>
       </c>
       <c r="K8" t="n">
-        <v>21400</v>
+        <v>3200</v>
       </c>
       <c r="L8" t="n">
-        <v>22300</v>
+        <v>3360</v>
       </c>
       <c r="M8" t="n">
-        <v>20050</v>
+        <v>2995</v>
       </c>
       <c r="N8" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>120141104590</v>
+        <v>36145755487</v>
       </c>
       <c r="P8" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q8" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R8" t="n">
-        <v>-64000</v>
+        <v>-8000</v>
       </c>
       <c r="S8" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대통령 지시로 주목받는 보안주 섹터의 수혜 기대. 금융 고객사 확보 및 샌즈랩, 안랩 등 타 종목 동반 상승 기대감.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '금융고객사', '샌즈랩']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18390</v>
+        <v>18370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.31%</t>
+          <t>'+3.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>523</v>
+        <v>589</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>180531444630</v>
+        <v>182669561525</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 루멘텀, 어플라이드옵토 등 동반 강세. 매물대 소화 및 2만원 돌파 기대.</t>
+          <t>미국 증시 광통신 섹터 강세 및 프로그램 매수세 유입에 따른 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '매물대', '공매도']</t>
+          <t>['광통신', '매물대', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17820</v>
+        <v>17780</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.19%</t>
+          <t>'+0.97%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="H10" t="n">
         <v>9.390000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>38714383335</v>
+        <v>39938487330</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>274250</v>
+        <v>274000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.63%</t>
+          <t>'-0.72%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>606</v>
+        <v>629</v>
       </c>
       <c r="F11" t="n">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="G11" t="n">
-        <v>2251</v>
+        <v>2295</v>
       </c>
       <c r="H11" t="n">
         <v>46.41</v>
@@ -1438,7 +1438,7 @@
         <v>46.41</v>
       </c>
       <c r="O11" t="n">
-        <v>1438919410000</v>
+        <v>1479118623750</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1793000</v>
+        <v>1792000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.61%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>462</v>
       </c>
       <c r="G12" t="n">
-        <v>2062</v>
+        <v>1970</v>
       </c>
       <c r="H12" t="n">
         <v>49.76</v>
@@ -1524,13 +1524,13 @@
         <v>1837000</v>
       </c>
       <c r="M12" t="n">
-        <v>1791000</v>
+        <v>1790000</v>
       </c>
       <c r="N12" t="n">
         <v>49.77</v>
       </c>
       <c r="O12" t="n">
-        <v>1946047046500</v>
+        <v>2032067757500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>엔비디아 및 미국 증시 신고가 경신에도 불구하고 메모리 관련주는 하락하는 모습. 일부 투자자 부정적 전망.</t>
+          <t>AI 열풍에도 불구하고 오너리스크 및 국장 악재로 인한 하락세 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['메모리', '엔비디아', '미국 증시']</t>
+          <t>['오너리스크', 'AI 열풍', '국장 악재']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261006_11.xlsx
+++ b/data/trending_integrated_20261006_11.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52561745260</v>
+        <v>52568419390</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18370</v>
+        <v>18190</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.60%</t>
+          <t>'+18.42%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H3" t="n">
         <v>2.17</v>
@@ -693,7 +693,7 @@
         <v>18000</v>
       </c>
       <c r="L3" t="n">
-        <v>18540</v>
+        <v>18550</v>
       </c>
       <c r="M3" t="n">
         <v>16800</v>
@@ -702,7 +702,7 @@
         <v>1.37</v>
       </c>
       <c r="O3" t="n">
-        <v>74503123255</v>
+        <v>81749174365</v>
       </c>
       <c r="P3" t="n">
         <v>38400</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47800</v>
+        <v>47650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.17%</t>
+          <t>'+17.80%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="F4" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G4" t="n">
-        <v>2980</v>
+        <v>3164</v>
       </c>
       <c r="H4" t="n">
         <v>14.1</v>
@@ -794,7 +794,7 @@
         <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>218854439775</v>
+        <v>221561241525</v>
       </c>
       <c r="P4" t="n">
         <v>69200</v>
@@ -810,12 +810,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 FDA 승인 관련 긍정적 소식과 MSCI 편입 기대감.</t>
+          <t>HLB 간암 신약 FDA 승인 기대감 고조. MSCI 편입 및 자금 유입 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4915</v>
+        <v>4895</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.70%</t>
+          <t>'+11.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>114954957711</v>
+        <v>117167796005</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20550</v>
+        <v>20450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.37%</t>
+          <t>'+8.83%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F6" t="n">
         <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
@@ -978,7 +978,7 @@
         <v>0.83</v>
       </c>
       <c r="O6" t="n">
-        <v>122053396740</v>
+        <v>123637464265</v>
       </c>
       <c r="P6" t="n">
         <v>30550</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.51%</t>
+          <t>'+8.58%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.17</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H7" t="n">
         <v>1.09</v>
@@ -1070,7 +1070,7 @@
         <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>18560687332</v>
+        <v>18776734330</v>
       </c>
       <c r="P7" t="n">
         <v>2970</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3085</v>
+        <v>3070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.44%</t>
+          <t>'+7.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.57</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H8" t="n">
         <v>1.82</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>36145755487</v>
+        <v>36769059789</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18370</v>
+        <v>18300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.20%</t>
+          <t>'+2.81%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>589</v>
+        <v>635</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>182669561525</v>
+        <v>185860808090</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 광통신 섹터 강세 및 프로그램 매수세 유입에 따른 기대감.</t>
+          <t>광통신 섹터 강세 및 프로그램 매수 유입 기대감. 매물 소화 후 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '매물대', '프로그램 매수']</t>
+          <t>['광통신', '프로그램 매수', '매물대']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1320,7 +1320,7 @@
         <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="H10" t="n">
         <v>9.390000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>39938487330</v>
+        <v>41064854290</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>274000</v>
+        <v>273000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.72%</t>
+          <t>'-1.09%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>629</v>
+        <v>664</v>
       </c>
       <c r="F11" t="n">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="G11" t="n">
-        <v>2295</v>
+        <v>2366</v>
       </c>
       <c r="H11" t="n">
         <v>46.41</v>
@@ -1432,13 +1432,13 @@
         <v>279000</v>
       </c>
       <c r="M11" t="n">
-        <v>274000</v>
+        <v>272500</v>
       </c>
       <c r="N11" t="n">
         <v>46.41</v>
       </c>
       <c r="O11" t="n">
-        <v>1479118623750</v>
+        <v>1544697447250</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1792000</v>
+        <v>1789000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="G12" t="n">
-        <v>1970</v>
+        <v>1875</v>
       </c>
       <c r="H12" t="n">
         <v>49.76</v>
@@ -1524,13 +1524,13 @@
         <v>1837000</v>
       </c>
       <c r="M12" t="n">
-        <v>1790000</v>
+        <v>1788000</v>
       </c>
       <c r="N12" t="n">
         <v>49.77</v>
       </c>
       <c r="O12" t="n">
-        <v>2032067757500</v>
+        <v>2133532606000</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 열풍에도 불구하고 오너리스크 및 국장 악재로 인한 하락세 우려.</t>
+          <t>오너 리스크 및 HBM, 솔리다임 관련 악재 부각. 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['오너리스크', 'AI 열풍', '국장 악재']</t>
+          <t>['오너 리스크', 'HBM', '솔리다임']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261006_11.xlsx
+++ b/data/trending_integrated_20261006_11.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52568419390</v>
+        <v>52596442930</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18190</v>
+        <v>47500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.42%</t>
+          <t>'+17.43%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>601</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>376</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>3230</v>
       </c>
       <c r="H3" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K3" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L3" t="n">
-        <v>18550</v>
+        <v>50700</v>
       </c>
       <c r="M3" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N3" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O3" t="n">
-        <v>81749174365</v>
+        <v>224132000800</v>
       </c>
       <c r="P3" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q3" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R3" t="n">
-        <v>41000</v>
+        <v>477000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>FDA 승인 관련 VAI(Verified AI) 정보 공개 및 간암 치료제 기대감에 따른 급등. MSCI 편입 예정으로 자금 유입 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['FDA', '승인', 'MSCI']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47650</v>
+        <v>17870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.80%</t>
+          <t>'+16.34%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>586</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>369</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>3164</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>14.1</v>
+        <v>2.17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>40450</v>
+        <v>15360</v>
       </c>
       <c r="K4" t="n">
-        <v>42700</v>
+        <v>18000</v>
       </c>
       <c r="L4" t="n">
-        <v>50700</v>
+        <v>18640</v>
       </c>
       <c r="M4" t="n">
-        <v>42150</v>
+        <v>16800</v>
       </c>
       <c r="N4" t="n">
-        <v>14.11</v>
+        <v>1.37</v>
       </c>
       <c r="O4" t="n">
-        <v>221561241525</v>
+        <v>89484100645</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>38400</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>8010</v>
       </c>
       <c r="R4" t="n">
-        <v>477000</v>
+        <v>41000</v>
       </c>
       <c r="S4" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HLB 간암 신약 FDA 승인 기대감 고조. MSCI 편입 및 자금 유입 전망.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['FDA 승인', '간암 신약', 'MSCI 편입']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4895</v>
+        <v>4920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.25%</t>
+          <t>'+11.82%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H5" t="n">
         <v>1.4</v>
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>117167796005</v>
+        <v>118726714301</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20450</v>
+        <v>1461</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.83%</t>
+          <t>'+9.03%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18790</v>
+        <v>1340</v>
       </c>
       <c r="K6" t="n">
-        <v>21400</v>
+        <v>1370</v>
       </c>
       <c r="L6" t="n">
-        <v>22300</v>
+        <v>1555</v>
       </c>
       <c r="M6" t="n">
-        <v>20050</v>
+        <v>1360</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>123637464265</v>
+        <v>18874445615</v>
       </c>
       <c r="P6" t="n">
-        <v>30550</v>
+        <v>2970</v>
       </c>
       <c r="Q6" t="n">
-        <v>6100</v>
+        <v>890</v>
       </c>
       <c r="R6" t="n">
-        <v>-64000</v>
+        <v>-15000</v>
       </c>
       <c r="S6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대통령 지시로 주목받는 보안주 섹터의 수혜 기대. 금융 고객사 확보 및 샌즈랩, 안랩 등 타 종목 동반 상승 기대감.</t>
+          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안주', '금융고객사', '샌즈랩']</t>
+          <t>['LNG', '송유관', '테마']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1455</v>
+        <v>20300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.58%</t>
+          <t>'+8.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1340</v>
+        <v>18790</v>
       </c>
       <c r="K7" t="n">
-        <v>1370</v>
+        <v>21400</v>
       </c>
       <c r="L7" t="n">
-        <v>1555</v>
+        <v>22300</v>
       </c>
       <c r="M7" t="n">
-        <v>1360</v>
+        <v>20050</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>18776734330</v>
+        <v>124742811515</v>
       </c>
       <c r="P7" t="n">
-        <v>2970</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>890</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-15000</v>
+        <v>-64000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
+          <t>보안주로서 금융기관 해킹 이슈와 연계된 성장 기대감. 2~3배 상승 전망 및 207곳 금융 고객사 보유. 하지만, 거래대금 및 경쟁사 비교 시 추가 상승 여력은 관망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['LNG', '송유관', '테마']</t>
+          <t>['보안주', '금융', '성장주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.91%</t>
+          <t>'+7.56%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H8" t="n">
         <v>1.82</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>36769059789</v>
+        <v>37073424239</v>
       </c>
       <c r="P8" t="n">
         <v>4810</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18300</v>
+        <v>18370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.81%</t>
+          <t>'+3.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
         <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="H9" t="n">
         <v>3.81</v>
@@ -1254,7 +1254,7 @@
         <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>185860808090</v>
+        <v>188615760980</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17780</v>
+        <v>17760</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.97%</t>
+          <t>'+0.85%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="H10" t="n">
         <v>9.390000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.449999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>41064854290</v>
+        <v>41886135250</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>273000</v>
+        <v>273500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.09%</t>
+          <t>'-0.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>664</v>
+        <v>710</v>
       </c>
       <c r="F11" t="n">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="G11" t="n">
-        <v>2366</v>
+        <v>2443</v>
       </c>
       <c r="H11" t="n">
         <v>46.41</v>
@@ -1432,13 +1432,13 @@
         <v>279000</v>
       </c>
       <c r="M11" t="n">
-        <v>272500</v>
+        <v>272000</v>
       </c>
       <c r="N11" t="n">
         <v>46.41</v>
       </c>
       <c r="O11" t="n">
-        <v>1544697447250</v>
+        <v>1617764234250</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 및 엔비디아 신고가 경신에 따른 반도체 시장 훈풍 기대감. 일부 부정적 뉴스 혼재.</t>
+          <t>반도체 시장 폭등 랠리 및 엔비디아 신고가 경신 속 외국인 매수 기대감. 다만, 실제 수급 및 실적 근거는 부족.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '엔비디아', '영업이익']</t>
+          <t>['반도체', '외국인', '엔비디아']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1789000</v>
+        <v>1793000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-2.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G12" t="n">
-        <v>1875</v>
+        <v>1854</v>
       </c>
       <c r="H12" t="n">
         <v>49.76</v>
@@ -1524,13 +1524,13 @@
         <v>1837000</v>
       </c>
       <c r="M12" t="n">
-        <v>1788000</v>
+        <v>1786000</v>
       </c>
       <c r="N12" t="n">
         <v>49.77</v>
       </c>
       <c r="O12" t="n">
-        <v>2133532606000</v>
+        <v>2209539580500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>오너 리스크 및 HBM, 솔리다임 관련 악재 부각. 주가 하락세 지속.</t>
+          <t>오너 리스크 및 솔리다임 상장 이슈로 인한 부정적 전망. ADR 대비 원주 외국인 수급 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['오너 리스크', 'HBM', '솔리다임']</t>
+          <t>['오너리스크', '솔리다임', '외국인']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261006_11.xlsx
+++ b/data/trending_integrated_20261006_11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G2" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>52596442930</v>
+        <v>52620966780</v>
       </c>
       <c r="P2" t="n">
         <v>22250</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>에스투더블유</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47500</v>
+        <v>18110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.43%</t>
+          <t>'+17.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
-        <v>601</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>376</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>3230</v>
+        <v>69</v>
       </c>
       <c r="H3" t="n">
-        <v>14.1</v>
+        <v>2.17</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40450</v>
+        <v>15360</v>
       </c>
       <c r="K3" t="n">
-        <v>42700</v>
+        <v>18000</v>
       </c>
       <c r="L3" t="n">
-        <v>50700</v>
+        <v>18640</v>
       </c>
       <c r="M3" t="n">
-        <v>42150</v>
+        <v>16800</v>
       </c>
       <c r="N3" t="n">
-        <v>14.11</v>
+        <v>1.37</v>
       </c>
       <c r="O3" t="n">
-        <v>224132000800</v>
+        <v>91995433385</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>38400</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>8010</v>
       </c>
       <c r="R3" t="n">
-        <v>477000</v>
+        <v>41000</v>
       </c>
       <c r="S3" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 VAI(Verified AI) 정보 공개 및 간암 치료제 기대감에 따른 급등. MSCI 편입 예정으로 자금 유입 전망.</t>
+          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA', '승인', 'MSCI']</t>
+          <t>['AI 보안', '대장주', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>488280</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>에스투더블유</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17870</v>
+        <v>47400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.34%</t>
+          <t>'+17.18%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>605</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>376</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>3343</v>
       </c>
       <c r="H4" t="n">
-        <v>2.17</v>
+        <v>14.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15360</v>
+        <v>40450</v>
       </c>
       <c r="K4" t="n">
-        <v>18000</v>
+        <v>42700</v>
       </c>
       <c r="L4" t="n">
-        <v>18640</v>
+        <v>50700</v>
       </c>
       <c r="M4" t="n">
-        <v>16800</v>
+        <v>42150</v>
       </c>
       <c r="N4" t="n">
-        <v>1.37</v>
+        <v>14.11</v>
       </c>
       <c r="O4" t="n">
-        <v>89484100645</v>
+        <v>224906246275</v>
       </c>
       <c r="P4" t="n">
-        <v>38400</v>
+        <v>69200</v>
       </c>
       <c r="Q4" t="n">
-        <v>8010</v>
+        <v>24150</v>
       </c>
       <c r="R4" t="n">
-        <v>41000</v>
+        <v>477000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 AI 보안주 급등 및 국내 보안주 테마 형성 속에서 에스투더블유의 대장주 역할 기대.</t>
+          <t>HLB 간암약 FDA 승인 가능성에 대한 AI 답변 및 블로그 게시글 언급. 동진결과, VAI 등을 근거로 제시하며 강력한 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '테마']</t>
+          <t>['FDA 승인', '간암약', 'VAI']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>488280</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4920</v>
+        <v>4895</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.82%</t>
+          <t>'+11.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>118726714301</v>
+        <v>119670611035</v>
       </c>
       <c r="P5" t="n">
         <v>8100</v>
@@ -931,123 +931,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KBI동양철관</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1461</v>
+        <v>20550</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.03%</t>
+          <t>'+9.37%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1340</v>
+        <v>18790</v>
       </c>
       <c r="K6" t="n">
-        <v>1370</v>
+        <v>21400</v>
       </c>
       <c r="L6" t="n">
-        <v>1555</v>
+        <v>22300</v>
       </c>
       <c r="M6" t="n">
-        <v>1360</v>
+        <v>20050</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>0.83</v>
       </c>
       <c r="O6" t="n">
-        <v>18874445615</v>
+        <v>125522340090</v>
       </c>
       <c r="P6" t="n">
-        <v>2970</v>
+        <v>30550</v>
       </c>
       <c r="Q6" t="n">
-        <v>890</v>
+        <v>6100</v>
       </c>
       <c r="R6" t="n">
-        <v>-15000</v>
+        <v>-64000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
+          <t>보안주로서 금융기관 해킹 이슈와 연계된 성장 기대감. 2~3배 상승 전망 및 207곳 금융 고객사 보유. 하지만, 거래대금 및 경쟁사 비교 시 추가 상승 여력은 관망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['LNG', '송유관', '테마']</t>
+          <t>['보안주', '금융', '성장주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>008970</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20300</v>
+        <v>3100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.04%</t>
+          <t>'+8.96%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18790</v>
+        <v>2845</v>
       </c>
       <c r="K7" t="n">
-        <v>21400</v>
+        <v>3200</v>
       </c>
       <c r="L7" t="n">
-        <v>22300</v>
+        <v>3360</v>
       </c>
       <c r="M7" t="n">
-        <v>20050</v>
+        <v>2995</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>124742811515</v>
+        <v>37659992851</v>
       </c>
       <c r="P7" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q7" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R7" t="n">
-        <v>-64000</v>
+        <v>-8000</v>
       </c>
       <c r="S7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보안주로서 금융기관 해킹 이슈와 연계된 성장 기대감. 2~3배 상승 전망 및 207곳 금융 고객사 보유. 하지만, 거래대금 및 경쟁사 비교 시 추가 상승 여력은 관망.</t>
+          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '금융', '성장주']</t>
+          <t>['CB', '차익실현', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,82 +1103,82 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3060</v>
+        <v>1448</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.56%</t>
+          <t>'+8.06%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.57</v>
+        <v>-0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2845</v>
+        <v>1340</v>
       </c>
       <c r="K8" t="n">
-        <v>3200</v>
+        <v>1370</v>
       </c>
       <c r="L8" t="n">
-        <v>3360</v>
+        <v>1555</v>
       </c>
       <c r="M8" t="n">
-        <v>2995</v>
+        <v>1360</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>37073424239</v>
+        <v>18973865879</v>
       </c>
       <c r="P8" t="n">
-        <v>4810</v>
+        <v>2970</v>
       </c>
       <c r="Q8" t="n">
-        <v>1400</v>
+        <v>890</v>
       </c>
       <c r="R8" t="n">
-        <v>-8000</v>
+        <v>-15000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>CB 남발 및 외인 차익 실현 매도로 인한 주가 하락세 지속, 타 보안주 이동 권유.</t>
+          <t>미국 부통령의 알래스카 LNG 사업 언급 및 한국 참여 의사 표명으로 인한 송유관 관련 사업 수혜 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['CB', '차익실현', '공매도']</t>
+          <t>['LNG', '송유관', '테마']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18370</v>
+        <v>15940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.20%</t>
+          <t>'+3.84%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F9" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>652</v>
+        <v>214</v>
       </c>
       <c r="H9" t="n">
-        <v>3.81</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17800</v>
+        <v>15350</v>
       </c>
       <c r="K9" t="n">
-        <v>18040</v>
+        <v>14920</v>
       </c>
       <c r="L9" t="n">
-        <v>18880</v>
+        <v>16590</v>
       </c>
       <c r="M9" t="n">
-        <v>17950</v>
+        <v>14300</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>0.18</v>
       </c>
       <c r="O9" t="n">
-        <v>188615760980</v>
+        <v>51095862885</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>29750</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>12760</v>
       </c>
       <c r="R9" t="n">
-        <v>679000</v>
+        <v>14000</v>
       </c>
       <c r="S9" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세 및 프로그램 매수 유입 기대감. 매물 소화 후 상승 전망.</t>
+          <t>기타법인의 자사주 매집 사실 언급. 광통신 섹터와의 연관성 및 통신 광원 반도체 독보적 기술 보유 등을 언급하며 상승 가능성 제시. 다만, 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '프로그램 매수', '매물대']</t>
+          <t>['자사주 매집', '광통신', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17760</v>
+        <v>18370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.85%</t>
+          <t>'+3.20%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>362</v>
+        <v>670</v>
       </c>
       <c r="H10" t="n">
-        <v>9.390000000000001</v>
+        <v>3.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17610</v>
+        <v>17800</v>
       </c>
       <c r="K10" t="n">
-        <v>17700</v>
+        <v>18040</v>
       </c>
       <c r="L10" t="n">
-        <v>18160</v>
+        <v>18880</v>
       </c>
       <c r="M10" t="n">
-        <v>17630</v>
+        <v>17950</v>
       </c>
       <c r="N10" t="n">
-        <v>9.449999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>41886135250</v>
+        <v>189947833065</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>381000</v>
+        <v>679000</v>
       </c>
       <c r="S10" t="n">
-        <v>-45000</v>
+        <v>-4000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주택 공급 확대 기사에도 불구하고, 원전 테마 언급 및 주가 누르기 의혹 제기로 인한 투자 심리 위축.</t>
+          <t>미국 증시 광통신 섹터 강세 및 루멘텀, 어플라이드옵토 등의 상승 언급. 3분기 영업이익 증가 및 현재 가격대 매물 소화 과정을 근거로 제시하며 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주택 공급', '원전 테마', '허매도']</t>
+          <t>['광통신', '영업이익', '매물대']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,43 +1379,43 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>273500</v>
+        <v>17760</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.91%</t>
+          <t>'+0.85%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>710</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>405</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>2443</v>
+        <v>375</v>
       </c>
       <c r="H11" t="n">
-        <v>46.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>276000</v>
+        <v>17610</v>
       </c>
       <c r="K11" t="n">
-        <v>278500</v>
+        <v>17700</v>
       </c>
       <c r="L11" t="n">
-        <v>279000</v>
+        <v>18160</v>
       </c>
       <c r="M11" t="n">
-        <v>272000</v>
+        <v>17630</v>
       </c>
       <c r="N11" t="n">
-        <v>46.41</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>1617764234250</v>
+        <v>42637693235</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>90200</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-779000</v>
+        <v>381000</v>
       </c>
       <c r="S11" t="n">
-        <v>311000</v>
+        <v>-45000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 시장 폭등 랠리 및 엔비디아 신고가 경신 속 외국인 매수 기대감. 다만, 실제 수급 및 실적 근거는 부족.</t>
+          <t>주택 공급 확대 기사에도 불구하고, 원전 테마 언급 및 주가 누르기 의혹 제기로 인한 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '엔비디아']</t>
+          <t>['주택 공급', '원전 테마', '허매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,43 +1471,43 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1793000</v>
+        <v>272000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.61%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>739</v>
       </c>
       <c r="F12" t="n">
-        <v>454</v>
+        <v>413</v>
       </c>
       <c r="G12" t="n">
-        <v>1854</v>
+        <v>2503</v>
       </c>
       <c r="H12" t="n">
-        <v>49.76</v>
+        <v>46.41</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1841000</v>
+        <v>276000</v>
       </c>
       <c r="K12" t="n">
-        <v>1835000</v>
+        <v>278500</v>
       </c>
       <c r="L12" t="n">
-        <v>1837000</v>
+        <v>279000</v>
       </c>
       <c r="M12" t="n">
-        <v>1786000</v>
+        <v>272000</v>
       </c>
       <c r="N12" t="n">
-        <v>49.77</v>
+        <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>2209539580500</v>
+        <v>1657321729750</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>-331000</v>
+        <v>-779000</v>
       </c>
       <c r="S12" t="n">
-        <v>38000</v>
+        <v>311000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>오너 리스크 및 솔리다임 상장 이슈로 인한 부정적 전망. ADR 대비 원주 외국인 수급 우려.</t>
+          <t>반도체 시장 급등 랠리 및 엔비디아 신고가 경신 등 호재 언급. 다만, 마이크론 하락 및 감정적 기대감 위주의 내용으로 fact_score는 보수적으로 산정.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['오너리스크', '솔리다임', '외국인']</t>
+          <t>['반도체', '엔비디아', '영업이익']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1567,6 +1567,98 @@
         </is>
       </c>
       <c r="Z12" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1789000</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-2.82%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E13" t="n">
+        <v>800</v>
+      </c>
+      <c r="F13" t="n">
+        <v>459</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1810</v>
+      </c>
+      <c r="H13" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1841000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1786000</v>
+      </c>
+      <c r="N13" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2274295006000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-331000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>38000</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>오너 리스크, 솔리다임 상장, HBM 기술 경쟁 등 악재 언급. ADR 및 국장 상황을 근거로 부정적 전망 제시. 감정적 비난과 부정적 전망이 주를 이룸.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['오너 리스크', '솔리다임', 'HBM']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>000660</t>
         </is>
